--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.70563379962069</v>
+        <v>9.702165492438363</v>
       </c>
       <c r="D2" t="n">
-        <v>60.09479314375721</v>
+        <v>9.765403885860547</v>
       </c>
       <c r="E2" t="n">
-        <v>23.4728276944675</v>
+        <v>3.81433450035097</v>
       </c>
       <c r="F2" t="n">
-        <v>23.78727931828796</v>
+        <v>3.865432889221795</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.22201604749304</v>
+        <v>5.886077607717619</v>
       </c>
       <c r="D3" t="n">
-        <v>36.2570847142524</v>
+        <v>5.891776266066016</v>
       </c>
       <c r="E3" t="n">
-        <v>23.4728276944675</v>
+        <v>3.81433450035097</v>
       </c>
       <c r="F3" t="n">
-        <v>23.78727931828796</v>
+        <v>3.865432889221795</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.80239442834072</v>
+        <v>4.680389094605367</v>
       </c>
       <c r="D4" t="n">
-        <v>28.40385696568688</v>
+        <v>4.615626756924119</v>
       </c>
       <c r="E4" t="n">
-        <v>23.4728276944675</v>
+        <v>3.81433450035097</v>
       </c>
       <c r="F4" t="n">
-        <v>23.78727931828796</v>
+        <v>3.865432889221795</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.586488769658351</v>
+        <v>1.557804425069482</v>
       </c>
       <c r="D5" t="n">
-        <v>9.603977278813579</v>
+        <v>1.560646307807207</v>
       </c>
       <c r="E5" t="n">
-        <v>23.4728276944675</v>
+        <v>3.81433450035097</v>
       </c>
       <c r="F5" t="n">
-        <v>23.78727931828796</v>
+        <v>3.865432889221795</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>76.39888799682306</v>
+        <v>12.41481929948375</v>
       </c>
       <c r="D6" t="n">
-        <v>77.14062435806274</v>
+        <v>12.5353514581852</v>
       </c>
       <c r="E6" t="n">
-        <v>23.4728276944675</v>
+        <v>3.81433450035097</v>
       </c>
       <c r="F6" t="n">
-        <v>23.78727931828796</v>
+        <v>3.865432889221795</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
